--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/이벤트 스크립트 테이블_1구역_ver5.5.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/이벤트 스크립트 테이블_1구역_ver5.5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200013\Desktop\프로젝트HI\2_Documents\데이터 테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F26E3C5F-2C0D-42F6-A52B-79037927D77E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBCBF5C-A800-486E-B08B-39810DFCD576}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="개요" sheetId="1" r:id="rId1"/>
@@ -6877,7 +6877,7 @@
         <v>1020010</v>
       </c>
       <c r="B2" s="59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="59"/>
       <c r="D2" s="59"/>
